--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAQ.xlsx
@@ -635,13 +635,13 @@
         <v>79.8</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
@@ -654,13 +654,13 @@
         <v>116.2</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -673,13 +673,13 @@
         <v>138.2</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>27.8</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="5">
@@ -692,13 +692,13 @@
         <v>-22</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>-22</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +711,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -736,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -749,7 +749,7 @@
         <v>0.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -768,13 +768,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="10">
@@ -790,7 +790,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -966,18 +966,6 @@
         </is>
       </c>
       <c r="B3" t="inlineStr">
-        <is>
-          <t>Win the first action: they do not consistently hurt teams with second-chance volume, so clean first stops carry value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Game Plan Keys</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
         <is>
           <t>Closeout discipline matters: A. Thiam are the first perimeter names you cannot lose in help situations.</t>
         </is>
@@ -1069,7 +1057,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAQ.xlsx
@@ -422,23 +422,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAQ_A._THIAM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. Thiam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -453,24 +824,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D. Bacchus | J. Shoats</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-7.6</v>
       </c>
     </row>
   </sheetData>
@@ -484,12 +913,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,34 +975,102 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>J. Shoats</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>base_lineup</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A. Thiam | D. Bacchus | I. Pavicevic | J. Shoats | J. Thomas (18.2 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A. Thiam | D. Bacchus | I. Pavicevic | J. Shoats | J. Thomas (8.8 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
         </is>
       </c>
     </row>
@@ -632,16 +1129,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1148,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116.2</v>
+        <v>113.7</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1167,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138.2</v>
+        <v>120.2</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>31.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1186,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-6.5</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>-21.6</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1205,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -733,10 +1230,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -746,16 +1243,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C8" t="n">
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -765,16 +1262,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="10">
@@ -784,16 +1281,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -809,10 +1306,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -853,7 +1350,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -877,7 +1374,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
         </is>
       </c>
     </row>
@@ -889,7 +1386,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -955,7 +1452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -966,6 +1463,30 @@
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>Finish possessions: the first stop is not enough against this team because the offensive glass is a real source of extra points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Load into J. Shoats: he is the main organizer, so make secondary creators finish possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Closeout discipline matters: A. Thiam are the first perimeter names you cannot lose in help situations.</t>
         </is>
@@ -982,7 +1503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1004,12 +1525,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Priority closeouts start with A. Thiam; do not lose them in help-and-recover situations.</t>
+          <t>The main offensive references are J. Shoats and A. Thiam; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1021,19 +1542,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from D. Horta and J. Thomas; contest, but do not over-help into secondary advantages.</t>
+          <t>Priority closeouts start with A. Thiam; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+          <t>Some perimeter volume comes from J. Thomas and D. Horta; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1045,29 +1566,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially A. Thiam, J. Shoats, and D. Bacchus; force them away from preferred areas.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Scoring Areas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Several players have clear comfort zones, especially A. Thiam, D. Horta, and J. Shoats; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: D. Bacchus | J. Shoats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Do not lose A. Thiam in help-and-recover situations.</t>
         </is>
@@ -1084,23 +1629,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAQ_A._THIAM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. Thiam</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1911,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1223,23 +2019,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1260,36 +2056,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1306,36 +2102,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1352,12 +2148,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAQ_A._HALLMAN</t>
+          <t>CAQ_J._CARNEIRO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Hallman</t>
+          <t>J. Carneiro</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1377,11 +2173,11 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1406,23 +2202,23 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -1442,23 +2238,23 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -1478,23 +2274,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
     </row>
@@ -1518,19 +2314,19 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -1554,19 +2350,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -1598,19 +2394,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -1622,12 +2418,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1638,23 +2434,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -1666,12 +2462,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1686,19 +2482,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1710,12 +2506,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1726,23 +2522,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +2550,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1770,23 +2566,67 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>83.3%</t>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>45.5%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAQ.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,59 +515,59 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAQ_A._THIAM</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Thiam</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -576,32 +576,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -619,16 +619,16 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -638,176 +638,280 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_A._THIAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>A. Thiam</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAQ_A._HALLMAN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A. Hallman</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAQ_D._RIDGNAL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Ridgnal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -824,11 +928,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -890,16 +994,74 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>47.5</v>
+        <v>67.8</v>
       </c>
       <c r="E2" t="n">
-        <v>94.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>101.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.6</v>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>J. Shoats | J. Thomas</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>J. Shoats | J. Thomas</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -1019,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Thiam | D. Bacchus | I. Pavicevic | J. Shoats | J. Thomas (18.2 min)</t>
+          <t>A. Thiam | D. Bacchus | I. Pavicevic | J. Shoats | J. Thomas (19.8 min)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Thiam | D. Bacchus | I. Pavicevic | J. Shoats | J. Thomas (8.8 net)</t>
+          <t>A. Thiam | D. Bacchus | I. Pavicevic | J. Shoats | J. Thomas (8.1 net)</t>
         </is>
       </c>
     </row>
@@ -1129,16 +1291,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -1148,16 +1310,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113.7</v>
+        <v>103.5</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>8.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="4">
@@ -1167,16 +1329,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>120.2</v>
+        <v>115.3</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>14.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="5">
@@ -1186,16 +1348,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6.5</v>
+        <v>-11.8</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.2</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="6">
@@ -1205,16 +1367,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -1230,10 +1392,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1243,16 +1405,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C8" t="n">
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1262,16 +1424,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="10">
@@ -1287,10 +1449,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1306,7 +1468,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1350,7 +1512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
+          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1524,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
+          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1536,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1548,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1560,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1572,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
+          <t>Less three-point dependent than league average; more of their offense is built away from pure perimeter volume.</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1614,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
+          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Finish possessions: the first stop is not enough against this team because the offensive glass is a real source of extra points.</t>
+          <t>Win the first action: they do not consistently hurt teams with second-chance volume, so clean first stops carry value.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1638,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Load into J. Shoats: he is the main organizer, so make secondary creators finish possessions.</t>
+          <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: A. Thiam are the first perimeter names you cannot lose in help situations.</t>
+          <t>Load into J. Shoats: he is the main organizer, so make secondary creators finish possessions.</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The main offensive references are J. Shoats and A. Thiam; load the scouting plan into those names first.</t>
+          <t>The main offensive references are J. Shoats and J. Thomas; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with A. Thiam; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with A. Thiam, D. Bacchus, and D. Horta; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1740,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially A. Thiam, D. Horta, and J. Shoats; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially A. Thiam, J. Shoats, and J. Thomas; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1752,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: D. Bacchus | J. Shoats.</t>
+          <t>Recognize the main duo/trio combinations: D. Bacchus | J. Shoats and J. Shoats | J. Thomas.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1764,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1776,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose A. Thiam in help-and-recover situations.</t>
+          <t>Do not lose A. Thiam and D. Bacchus in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1858,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1723,36 +1885,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAQ_A._THIAM</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Thiam</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>28.9</v>
       </c>
       <c r="D3" t="n">
-        <v>19.5</v>
+        <v>11.3</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
@@ -1768,17 +1930,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4</v>
+        <v>26.6</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>10.7</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1795,108 +1957,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_A._THIAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>A. Thiam</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.4</v>
+        <v>24.4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="D6" t="n">
-        <v>11.5</v>
+        <v>6.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1911,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2019,7 +2181,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2028,11 +2190,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -2051,41 +2213,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2097,7 +2259,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2111,23 +2273,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2143,41 +2305,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAQ_J._CARNEIRO</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Carneiro</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2189,146 +2351,186 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>40</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>32.5%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>30.3%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>38</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>52.6%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>28.8%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>32</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>24.2%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAQ_A._HALLMAN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A. Hallman</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2346,42 +2548,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CAQ_A._THIAM</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>A. Thiam</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -2390,42 +2584,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CAQ_D._HORTA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>D. Horta</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2434,42 +2620,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CAQ_J._SHOATS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>J. Shoats</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2478,42 +2656,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CAQ_D._BACCHUS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>D. Bacchus</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2522,23 +2692,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2720,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_A._THIAM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>A. Thiam</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2566,23 +2736,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2764,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2610,23 +2780,243 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>13</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>45.5%</t>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAQ_A._HALLMAN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A. Hallman</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>35.3%</t>
         </is>
       </c>
     </row>
